--- a/artfynd/A 33711-2023 artfynd.xlsx
+++ b/artfynd/A 33711-2023 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136796926</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136796919</v>
       </c>
       <c r="B5" t="n">
-        <v>92290</v>
+        <v>92292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136796929</v>
       </c>
       <c r="B6" t="n">
-        <v>92033</v>
+        <v>92035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136796921</v>
       </c>
       <c r="B7" t="n">
-        <v>93435</v>
+        <v>93437</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33711-2023 artfynd.xlsx
+++ b/artfynd/A 33711-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136796923</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136796928</v>
       </c>
       <c r="B3" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136796926</v>
       </c>
       <c r="B4" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136796919</v>
       </c>
       <c r="B5" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136796929</v>
       </c>
       <c r="B6" t="n">
-        <v>92035</v>
+        <v>92037</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136796921</v>
       </c>
       <c r="B7" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136796932</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136796917</v>
       </c>
       <c r="B9" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136796922</v>
       </c>
       <c r="B10" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136796924</v>
       </c>
       <c r="B11" t="n">
-        <v>80485</v>
+        <v>80489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136796913</v>
       </c>
       <c r="B12" t="n">
-        <v>80602</v>
+        <v>80606</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136796914</v>
       </c>
       <c r="B15" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33711-2023 artfynd.xlsx
+++ b/artfynd/A 33711-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136796923</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136796928</v>
       </c>
       <c r="B3" t="n">
-        <v>80458</v>
+        <v>80460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136796926</v>
       </c>
       <c r="B4" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136796919</v>
       </c>
       <c r="B5" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136796929</v>
       </c>
       <c r="B6" t="n">
-        <v>92037</v>
+        <v>92039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136796921</v>
       </c>
       <c r="B7" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136796932</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136796917</v>
       </c>
       <c r="B9" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136796922</v>
       </c>
       <c r="B10" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136796924</v>
       </c>
       <c r="B11" t="n">
-        <v>80489</v>
+        <v>80491</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136796913</v>
       </c>
       <c r="B12" t="n">
-        <v>80606</v>
+        <v>80608</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136796915</v>
       </c>
       <c r="B13" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136796914</v>
       </c>
       <c r="B15" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33711-2023 artfynd.xlsx
+++ b/artfynd/A 33711-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136796923</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136796928</v>
       </c>
       <c r="B3" t="n">
-        <v>80460</v>
+        <v>80461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136796926</v>
       </c>
       <c r="B4" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136796919</v>
       </c>
       <c r="B5" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136796929</v>
       </c>
       <c r="B6" t="n">
-        <v>92039</v>
+        <v>92040</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136796921</v>
       </c>
       <c r="B7" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136796932</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136796917</v>
       </c>
       <c r="B9" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136796922</v>
       </c>
       <c r="B10" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136796924</v>
       </c>
       <c r="B11" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136796913</v>
       </c>
       <c r="B12" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136796915</v>
       </c>
       <c r="B13" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136796914</v>
       </c>
       <c r="B15" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33711-2023 artfynd.xlsx
+++ b/artfynd/A 33711-2023 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136796926</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136796919</v>
       </c>
       <c r="B5" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136796929</v>
       </c>
       <c r="B6" t="n">
-        <v>92040</v>
+        <v>92046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136796921</v>
       </c>
       <c r="B7" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33711-2023 artfynd.xlsx
+++ b/artfynd/A 33711-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136796923</v>
       </c>
       <c r="B2" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136796928</v>
       </c>
       <c r="B3" t="n">
-        <v>80461</v>
+        <v>80463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136796926</v>
       </c>
       <c r="B4" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136796919</v>
       </c>
       <c r="B5" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136796929</v>
       </c>
       <c r="B6" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136796921</v>
       </c>
       <c r="B7" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136796932</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136796917</v>
       </c>
       <c r="B9" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136796922</v>
       </c>
       <c r="B10" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136796924</v>
       </c>
       <c r="B11" t="n">
-        <v>80492</v>
+        <v>80494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136796913</v>
       </c>
       <c r="B12" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136796915</v>
       </c>
       <c r="B13" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136796914</v>
       </c>
       <c r="B15" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33711-2023 artfynd.xlsx
+++ b/artfynd/A 33711-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136796923</v>
       </c>
       <c r="B2" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136796928</v>
       </c>
       <c r="B3" t="n">
-        <v>80463</v>
+        <v>80466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136796926</v>
       </c>
       <c r="B4" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136796919</v>
       </c>
       <c r="B5" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136796929</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136796921</v>
       </c>
       <c r="B7" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136796932</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136796917</v>
       </c>
       <c r="B9" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136796922</v>
       </c>
       <c r="B10" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136796924</v>
       </c>
       <c r="B11" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136796913</v>
       </c>
       <c r="B12" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136796915</v>
       </c>
       <c r="B13" t="n">
-        <v>78485</v>
+        <v>78488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136796914</v>
       </c>
       <c r="B15" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33711-2023 artfynd.xlsx
+++ b/artfynd/A 33711-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136796923</v>
       </c>
       <c r="B2" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136796928</v>
       </c>
       <c r="B3" t="n">
-        <v>80466</v>
+        <v>80479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136796926</v>
       </c>
       <c r="B4" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136796919</v>
       </c>
       <c r="B5" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136796929</v>
       </c>
       <c r="B6" t="n">
-        <v>92052</v>
+        <v>92065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136796921</v>
       </c>
       <c r="B7" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136796932</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136796917</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136796922</v>
       </c>
       <c r="B10" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136796924</v>
       </c>
       <c r="B11" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136796913</v>
       </c>
       <c r="B12" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136796915</v>
       </c>
       <c r="B13" t="n">
-        <v>78488</v>
+        <v>78501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136796916</v>
       </c>
       <c r="B14" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136796914</v>
       </c>
       <c r="B15" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33711-2023 artfynd.xlsx
+++ b/artfynd/A 33711-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136796923</v>
       </c>
       <c r="B2" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136796928</v>
       </c>
       <c r="B3" t="n">
-        <v>80479</v>
+        <v>80481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136796926</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136796919</v>
       </c>
       <c r="B5" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136796929</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136796921</v>
       </c>
       <c r="B7" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136796932</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136796917</v>
       </c>
       <c r="B9" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136796922</v>
       </c>
       <c r="B10" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136796924</v>
       </c>
       <c r="B11" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136796913</v>
       </c>
       <c r="B12" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136796915</v>
       </c>
       <c r="B13" t="n">
-        <v>78501</v>
+        <v>78503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136796916</v>
       </c>
       <c r="B14" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136796914</v>
       </c>
       <c r="B15" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33711-2023 artfynd.xlsx
+++ b/artfynd/A 33711-2023 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136796926</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136796919</v>
       </c>
       <c r="B5" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136796929</v>
       </c>
       <c r="B6" t="n">
-        <v>92067</v>
+        <v>92070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136796921</v>
       </c>
       <c r="B7" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33711-2023 artfynd.xlsx
+++ b/artfynd/A 33711-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136796923</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136796928</v>
       </c>
       <c r="B3" t="n">
-        <v>80481</v>
+        <v>80491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136796926</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136796919</v>
       </c>
       <c r="B5" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136796929</v>
       </c>
       <c r="B6" t="n">
-        <v>92070</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136796921</v>
       </c>
       <c r="B7" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136796932</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136796917</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136796922</v>
       </c>
       <c r="B10" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136796924</v>
       </c>
       <c r="B11" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136796913</v>
       </c>
       <c r="B12" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136796915</v>
       </c>
       <c r="B13" t="n">
-        <v>78503</v>
+        <v>78513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136796916</v>
       </c>
       <c r="B14" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136796914</v>
       </c>
       <c r="B15" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33711-2023 artfynd.xlsx
+++ b/artfynd/A 33711-2023 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136796926</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136796919</v>
       </c>
       <c r="B5" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136796929</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136796921</v>
       </c>
       <c r="B7" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33711-2023 artfynd.xlsx
+++ b/artfynd/A 33711-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136796923</v>
       </c>
       <c r="B2" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136796928</v>
       </c>
       <c r="B3" t="n">
-        <v>80491</v>
+        <v>80494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136796926</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136796919</v>
       </c>
       <c r="B5" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136796929</v>
       </c>
       <c r="B6" t="n">
-        <v>92081</v>
+        <v>92084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136796921</v>
       </c>
       <c r="B7" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136796932</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136796917</v>
       </c>
       <c r="B9" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136796922</v>
       </c>
       <c r="B10" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136796924</v>
       </c>
       <c r="B11" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136796913</v>
       </c>
       <c r="B12" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136796915</v>
       </c>
       <c r="B13" t="n">
-        <v>78513</v>
+        <v>78516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136796916</v>
       </c>
       <c r="B14" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136796914</v>
       </c>
       <c r="B15" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 33711-2023 artfynd.xlsx
+++ b/artfynd/A 33711-2023 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136796926</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136796919</v>
       </c>
       <c r="B5" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136796929</v>
       </c>
       <c r="B6" t="n">
-        <v>92084</v>
+        <v>92086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136796921</v>
       </c>
       <c r="B7" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33711-2023 artfynd.xlsx
+++ b/artfynd/A 33711-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136796923</v>
       </c>
       <c r="B2" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136796928</v>
       </c>
       <c r="B3" t="n">
-        <v>80494</v>
+        <v>80499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136796926</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136796919</v>
       </c>
       <c r="B5" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136796929</v>
       </c>
       <c r="B6" t="n">
-        <v>92086</v>
+        <v>92091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136796921</v>
       </c>
       <c r="B7" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136796932</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136796917</v>
       </c>
       <c r="B9" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136796922</v>
       </c>
       <c r="B10" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136796924</v>
       </c>
       <c r="B11" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136796913</v>
       </c>
       <c r="B12" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>136796915</v>
       </c>
       <c r="B13" t="n">
-        <v>78516</v>
+        <v>78521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>136796916</v>
       </c>
       <c r="B14" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136796914</v>
       </c>
       <c r="B15" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
